--- a/data/trans_dic/P19C06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,21</t>
+          <t>0,08; 1,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,74</t>
+          <t>0,17; 1,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,98</t>
+          <t>0,79; 3,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,57</t>
+          <t>0,45; 2,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,62</t>
+          <t>0,46; 1,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,14</t>
+          <t>0,27; 1,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,66</t>
+          <t>0,44; 1,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,7</t>
+          <t>0,39; 1,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,11</t>
+          <t>0,34; 1,12</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,67</t>
+          <t>0,74; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,81</t>
+          <t>0,75; 2,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,08</t>
+          <t>0,51; 1,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,58</t>
+          <t>0,33; 2,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,49</t>
+          <t>0,62; 2,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,29</t>
+          <t>0,62; 2,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,39</t>
+          <t>0,31; 1,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,03</t>
+          <t>0,66; 2,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,13</t>
+          <t>0,87; 2,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,17</t>
+          <t>0,9; 2,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,51</t>
+          <t>0,53; 1,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,91</t>
+          <t>0,59; 1,97</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,97</t>
+          <t>0,35; 1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,85</t>
+          <t>0,3; 1,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,67</t>
+          <t>0,78; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,5</t>
+          <t>0,24; 1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,67</t>
+          <t>0,75; 2,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,01</t>
+          <t>0,8; 2,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,93</t>
+          <t>0,33; 1,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,72</t>
+          <t>0,4; 1,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,01</t>
+          <t>0,67; 1,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,07</t>
+          <t>0,72; 2,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,24</t>
+          <t>0,72; 2,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,42</t>
+          <t>0,46; 1,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,54</t>
+          <t>0,62; 2,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,24</t>
+          <t>0,51; 2,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,25</t>
+          <t>0,59; 2,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,82</t>
+          <t>0,41; 1,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,79</t>
+          <t>0,47; 1,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,11</t>
+          <t>0,66; 2,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,63</t>
+          <t>1,53; 3,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,72</t>
+          <t>0,63; 1,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,75</t>
+          <t>0,72; 1,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,86</t>
+          <t>0,81; 1,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,65</t>
+          <t>1,19; 2,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,51</t>
+          <t>0,66; 1,51</t>
         </is>
       </c>
     </row>
@@ -1277,57 +1277,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,56</t>
+          <t>0,76; 1,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,48</t>
+          <t>0,66; 1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,73</t>
+          <t>0,77; 1,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,33</t>
+          <t>0,53; 1,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,57</t>
+          <t>0,79; 1,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,96</t>
+          <t>1,05; 1,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,83</t>
+          <t>0,96; 1,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,41</t>
+          <t>0,76; 1,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,45</t>
+          <t>0,85; 1,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,52</t>
+          <t>0,97; 1,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,59</t>
+          <t>0,99; 1,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7870</t>
+          <t>0; 6062</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6826</t>
+          <t>0; 6563</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9468</t>
+          <t>0; 9412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>532; 7388</t>
+          <t>512; 7222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>941; 9340</t>
+          <t>923; 9283</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4444; 18942</t>
+          <t>5017; 19073</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2359; 14012</t>
+          <t>2423; 13523</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2804; 10582</t>
+          <t>2976; 11424</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1932; 11549</t>
+          <t>2707; 12013</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6244; 20607</t>
+          <t>5490; 20374</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3826; 18219</t>
+          <t>4200; 18426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4311; 13975</t>
+          <t>4341; 14195</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5409; 19298</t>
+          <t>5360; 19052</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6916; 24356</t>
+          <t>6528; 22615</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4465; 17015</t>
+          <t>4135; 16135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4038; 30090</t>
+          <t>3844; 29430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5339; 20042</t>
+          <t>4996; 18906</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6256; 20610</t>
+          <t>5554; 19887</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2105; 12065</t>
+          <t>2721; 12793</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6325; 19152</t>
+          <t>6226; 19496</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12884; 32535</t>
+          <t>13271; 33251</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16888; 38376</t>
+          <t>15809; 36408</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8905; 25400</t>
+          <t>8989; 24085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12962; 40290</t>
+          <t>12466; 41510</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1900; 10739</t>
+          <t>1903; 10869</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1890; 11779</t>
+          <t>1898; 11522</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5050; 20191</t>
+          <t>4320; 19808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1884; 10328</t>
+          <t>1640; 9620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3996; 15629</t>
+          <t>4395; 15258</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6225; 20427</t>
+          <t>5432; 19982</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1908; 11161</t>
+          <t>1932; 11136</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3394; 15821</t>
+          <t>3718; 15030</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7700; 22723</t>
+          <t>7589; 22183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9860; 27268</t>
+          <t>9405; 27287</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8519; 25324</t>
+          <t>8140; 26396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7088; 22782</t>
+          <t>7385; 21599</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5093; 18038</t>
+          <t>4404; 16285</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4418; 18024</t>
+          <t>4135; 17429</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4314; 17362</t>
+          <t>4523; 17424</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3955; 16174</t>
+          <t>3619; 14940</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3823; 14560</t>
+          <t>3850; 15201</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6206; 19671</t>
+          <t>6172; 21506</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13298; 31852</t>
+          <t>13444; 32192</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6612; 18326</t>
+          <t>6741; 18768</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10790; 26639</t>
+          <t>10908; 26498</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13371; 32282</t>
+          <t>14143; 32449</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20277; 43675</t>
+          <t>19617; 41677</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12987; 29461</t>
+          <t>12903; 29484</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18164; 38256</t>
+          <t>18548; 38698</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20054; 43082</t>
+          <t>19176; 43009</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21809; 46014</t>
+          <t>20435; 45366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16831; 44629</t>
+          <t>17637; 47547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21919; 43006</t>
+          <t>21592; 42782</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33303; 61523</t>
+          <t>32881; 60713</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25919; 52492</t>
+          <t>27394; 51842</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27131; 50506</t>
+          <t>27140; 49962</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44581; 75159</t>
+          <t>43972; 74330</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57445; 91903</t>
+          <t>58938; 96114</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53556; 87748</t>
+          <t>54526; 88150</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49680; 87707</t>
+          <t>50028; 88190</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C06-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,18</t>
+          <t>0,08; 1,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,73</t>
+          <t>0,17; 1,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,0</t>
+          <t>0,77; 2,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,48</t>
+          <t>0,51; 2,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,75</t>
+          <t>0,52; 1,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,18</t>
+          <t>0,19; 1,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,64</t>
+          <t>0,51; 1,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,72</t>
+          <t>0,4; 1,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,12</t>
+          <t>0,35; 1,15</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,64</t>
+          <t>0,74; 2,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,61</t>
+          <t>0,77; 2,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,98</t>
+          <t>0,51; 2,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,52</t>
+          <t>0,48; 2,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,35</t>
+          <t>0,65; 2,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,21</t>
+          <t>0,69; 2,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,48</t>
+          <t>0,25; 1,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,07</t>
+          <t>0,63; 1,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,18</t>
+          <t>0,84; 2,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,06</t>
+          <t>0,86; 2,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,43</t>
+          <t>0,5; 1,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,97</t>
+          <t>0,68; 1,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,99</t>
+          <t>0,34; 1,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,81</t>
+          <t>0,31; 2,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,6</t>
+          <t>0,77; 3,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,4</t>
+          <t>0,24; 1,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,61</t>
+          <t>0,7; 2,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,95</t>
+          <t>0,87; 2,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,92</t>
+          <t>0,33; 1,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,63</t>
+          <t>0,72; 2,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,96</t>
+          <t>0,64; 1,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,08</t>
+          <t>0,74; 2,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,34</t>
+          <t>0,78; 2,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,34</t>
+          <t>0,6; 1,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,29</t>
+          <t>0,62; 2,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,16</t>
+          <t>0,58; 2,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,26</t>
+          <t>0,65; 2,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,68</t>
+          <t>0,4; 1,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,87</t>
+          <t>0,47; 1,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,3</t>
+          <t>0,64; 2,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,67</t>
+          <t>1,44; 3,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,77</t>
+          <t>0,64; 1,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,74</t>
+          <t>0,72; 1,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,87</t>
+          <t>0,77; 1,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,53</t>
+          <t>1,24; 2,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,51</t>
+          <t>0,63; 1,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,58</t>
+          <t>0,73; 1,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,48</t>
+          <t>0,66; 1,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,7</t>
+          <t>0,78; 1,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,42</t>
+          <t>0,49; 1,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,56</t>
+          <t>0,79; 1,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,93</t>
+          <t>1,03; 1,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,81</t>
+          <t>0,95; 1,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,4</t>
+          <t>0,86; 1,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,43</t>
+          <t>0,86; 1,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,59</t>
+          <t>0,95; 1,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,59</t>
+          <t>1,0; 1,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,27</t>
+          <t>0,75; 1,17</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>9174</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6062</t>
+          <t>0; 7014</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6563</t>
+          <t>0; 7248</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9412</t>
+          <t>0; 10049</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512; 7222</t>
+          <t>510; 6899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>923; 9283</t>
+          <t>933; 9187</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5017; 19073</t>
+          <t>4911; 18344</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2423; 13523</t>
+          <t>2782; 13527</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2976; 11424</t>
+          <t>3650; 12111</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2707; 12013</t>
+          <t>1936; 11451</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5490; 20374</t>
+          <t>6367; 21670</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4200; 18426</t>
+          <t>4256; 17451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4341; 14195</t>
+          <t>4733; 15763</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>21999</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5360; 19052</t>
+          <t>5340; 19455</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6528; 22615</t>
+          <t>6638; 23328</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4135; 16135</t>
+          <t>4129; 17931</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3844; 29430</t>
+          <t>4871; 22652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4996; 18906</t>
+          <t>5233; 18449</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5554; 19887</t>
+          <t>6202; 20888</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2721; 12793</t>
+          <t>2137; 12247</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6226; 19496</t>
+          <t>6602; 19110</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13271; 33251</t>
+          <t>12819; 32498</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15809; 36408</t>
+          <t>15194; 36961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8989; 24085</t>
+          <t>8417; 24633</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12466; 41510</t>
+          <t>13964; 35434</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>14979</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1903; 10869</t>
+          <t>1853; 10649</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1898; 11522</t>
+          <t>1942; 13258</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4320; 19808</t>
+          <t>4227; 19562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1640; 9620</t>
+          <t>1835; 11012</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4395; 15258</t>
+          <t>4081; 15522</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5432; 19982</t>
+          <t>5890; 20171</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1932; 11136</t>
+          <t>1912; 10811</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3718; 15030</t>
+          <t>5692; 16578</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7589; 22183</t>
+          <t>7250; 21276</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9405; 27287</t>
+          <t>9735; 26974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8140; 26396</t>
+          <t>8824; 25571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7385; 21599</t>
+          <t>9442; 23005</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>19664</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4404; 16285</t>
+          <t>4398; 16155</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4135; 17429</t>
+          <t>4687; 17143</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4523; 17424</t>
+          <t>5054; 19762</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3619; 14940</t>
+          <t>3777; 14390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3850; 15201</t>
+          <t>3819; 15138</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6172; 21506</t>
+          <t>5927; 20466</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13444; 32192</t>
+          <t>12623; 31410</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6741; 18768</t>
+          <t>6936; 18468</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10908; 26498</t>
+          <t>11035; 27596</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14143; 32449</t>
+          <t>13402; 31902</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19617; 41677</t>
+          <t>20527; 43900</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12903; 29484</t>
+          <t>12835; 28522</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65599</t>
+          <t>65816</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18548; 38698</t>
+          <t>17947; 39477</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19176; 43009</t>
+          <t>19331; 42640</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20435; 45366</t>
+          <t>20681; 46112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17637; 47547</t>
+          <t>16717; 38755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21592; 42782</t>
+          <t>21766; 43025</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32881; 60713</t>
+          <t>32266; 60387</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27394; 51842</t>
+          <t>27304; 51039</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27140; 49962</t>
+          <t>31072; 51186</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43972; 74330</t>
+          <t>44777; 75670</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58938; 96114</t>
+          <t>57838; 91307</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54526; 88150</t>
+          <t>55441; 89976</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50028; 88190</t>
+          <t>52408; 82327</t>
         </is>
       </c>
     </row>
